--- a/pipeline/credit_rating/output/saigonratings_xhtn_20261001.xlsx
+++ b/pipeline/credit_rating/output/saigonratings_xhtn_20261001.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S2" s="1" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
@@ -699,7 +699,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -833,7 +833,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
@@ -900,7 +900,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
@@ -967,7 +967,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S9" s="1" t="n">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S28" s="1" t="n">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S33" s="1" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S55" s="1" t="n">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S72" s="1" t="n">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S88" s="1" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S89" s="1" t="n">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S90" s="1" t="n">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S91" s="1" t="n">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S92" s="1" t="n">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S93" s="1" t="n">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S94" s="1" t="n">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S95" s="1" t="n">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S96" s="1" t="n">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S97" s="1" t="n">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S98" s="1" t="n">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S99" s="1" t="n">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S100" s="1" t="n">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S101" s="1" t="n">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S102" s="1" t="n">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S103" s="1" t="n">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S104" s="1" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S105" s="1" t="n">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S106" s="1" t="n">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S107" s="1" t="n">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S108" s="1" t="n">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S109" s="1" t="n">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S110" s="1" t="n">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S111" s="1" t="n">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S112" s="1" t="n">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S113" s="1" t="n">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S114" s="1" t="n">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S115" s="1" t="n">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S116" s="1" t="n">
@@ -8390,7 +8390,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S117" s="1" t="n">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S118" s="1" t="n">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S119" s="1" t="n">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S120" s="1" t="n">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S121" s="1" t="n">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S122" s="1" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S123" s="1" t="n">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S124" s="1" t="n">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S125" s="1" t="n">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S126" s="1" t="n">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S127" s="1" t="n">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S128" s="1" t="n">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S129" s="1" t="n">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S130" s="1" t="n">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S131" s="1" t="n">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S132" s="1" t="n">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S133" s="1" t="n">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S134" s="1" t="n">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S135" s="1" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S136" s="1" t="n">
@@ -9730,7 +9730,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S137" s="1" t="n">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S138" s="1" t="n">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S139" s="1" t="n">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S140" s="1" t="n">
@@ -9998,7 +9998,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S141" s="1" t="n">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S142" s="1" t="n">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S143" s="1" t="n">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S144" s="1" t="n">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S145" s="1" t="n">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S146" s="1" t="n">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S147" s="1" t="n">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S148" s="1" t="n">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S149" s="1" t="n">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S150" s="1" t="n">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S151" s="1" t="n">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S152" s="1" t="n">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S153" s="1" t="n">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S154" s="1" t="n">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S155" s="1" t="n">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S156" s="1" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S157" s="1" t="n">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S158" s="1" t="n">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S159" s="1" t="n">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S160" s="1" t="n">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S161" s="1" t="n">
@@ -11417,7 +11417,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S162" s="1" t="n">
@@ -11484,7 +11484,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S163" s="1" t="n">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S164" s="1" t="n">
@@ -11618,7 +11618,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S165" s="1" t="n">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S166" s="1" t="n">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S167" s="1" t="n">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S168" s="1" t="n">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S169" s="1" t="n">
@@ -11953,7 +11953,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S170" s="1" t="n">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S171" s="1" t="n">
@@ -12087,7 +12087,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S172" s="1" t="n">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S173" s="1" t="n">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S174" s="1" t="n">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S175" s="1" t="n">
@@ -12355,7 +12355,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S176" s="1" t="n">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S177" s="1" t="n">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S178" s="1" t="n">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S179" s="1" t="n">
@@ -12623,7 +12623,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S180" s="1" t="n">
@@ -12690,7 +12690,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S181" s="1" t="n">
@@ -12757,7 +12757,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S182" s="1" t="n">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S183" s="1" t="n">
@@ -12891,7 +12891,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S184" s="1" t="n">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S185" s="1" t="n">
@@ -13025,7 +13025,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S186" s="1" t="n">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S187" s="1" t="n">
@@ -13159,7 +13159,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S188" s="1" t="n">
@@ -13226,7 +13226,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S189" s="1" t="n">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S190" s="1" t="n">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S191" s="1" t="n">
@@ -13427,7 +13427,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S192" s="1" t="n">
@@ -13494,7 +13494,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S193" s="1" t="n">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S194" s="1" t="n">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S195" s="1" t="n">
@@ -13695,7 +13695,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S196" s="1" t="n">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S197" s="1" t="n">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S198" s="1" t="n">
@@ -13896,7 +13896,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S199" s="1" t="n">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S200" s="1" t="n">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S201" s="1" t="n">
@@ -14097,7 +14097,7 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S202" s="1" t="n">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S203" s="1" t="n">
@@ -14231,7 +14231,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S204" s="1" t="n">
@@ -14302,7 +14302,7 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S205" s="1" t="n">
@@ -14369,7 +14369,7 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S206" s="1" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S207" s="1" t="n">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S208" s="1" t="n">
@@ -14570,7 +14570,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S209" s="1" t="n">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S210" s="1" t="n">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S211" s="1" t="n">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S212" s="1" t="n">
@@ -14838,7 +14838,7 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S213" s="1" t="n">
@@ -14905,7 +14905,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S214" s="1" t="n">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S215" s="1" t="n">
@@ -15039,7 +15039,7 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S216" s="1" t="n">
@@ -15106,7 +15106,7 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S217" s="1" t="n">
@@ -15173,7 +15173,7 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S218" s="1" t="n">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S219" s="1" t="n">
@@ -15307,7 +15307,7 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S220" s="1" t="n">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S221" s="1" t="n">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S222" s="1" t="n">
@@ -15508,7 +15508,7 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S223" s="1" t="n">
@@ -15575,7 +15575,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S224" s="1" t="n">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S225" s="1" t="n">
@@ -15709,7 +15709,7 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S226" s="1" t="n">
@@ -15776,7 +15776,7 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S227" s="1" t="n">
@@ -15843,7 +15843,7 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S228" s="1" t="n">
@@ -15910,7 +15910,7 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S229" s="1" t="n">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S230" s="1" t="n">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S231" s="1" t="n">
@@ -16111,7 +16111,7 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S232" s="1" t="n">
@@ -16178,7 +16178,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S233" s="1" t="n">
@@ -16245,7 +16245,7 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S234" s="1" t="n">
@@ -16312,7 +16312,7 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S235" s="1" t="n">
@@ -16379,7 +16379,7 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S236" s="1" t="n">
@@ -16446,7 +16446,7 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S237" s="1" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S238" s="1" t="n">
@@ -16580,7 +16580,7 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S239" s="1" t="n">
@@ -16647,7 +16647,7 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S240" s="1" t="n">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S241" s="1" t="n">
@@ -16781,7 +16781,7 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S242" s="1" t="n">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S243" s="1" t="n">
@@ -16915,7 +16915,7 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S244" s="1" t="n">
@@ -16982,7 +16982,7 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S245" s="1" t="n">
@@ -17049,7 +17049,7 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S246" s="1" t="n">
@@ -17116,7 +17116,7 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S247" s="1" t="n">
@@ -17183,7 +17183,7 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S248" s="1" t="n">
@@ -17250,7 +17250,7 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S249" s="1" t="n">
@@ -17317,7 +17317,7 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S250" s="1" t="n">
@@ -17384,7 +17384,7 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S251" s="1" t="n">
@@ -17451,7 +17451,7 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S252" s="1" t="n">
@@ -17518,7 +17518,7 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S253" s="1" t="n">
@@ -17585,7 +17585,7 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S254" s="1" t="n">
@@ -17652,7 +17652,7 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S255" s="1" t="n">
@@ -17719,7 +17719,7 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S256" s="1" t="n">
@@ -17786,7 +17786,7 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S257" s="1" t="n">
@@ -17853,7 +17853,7 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S258" s="1" t="n">
@@ -17920,7 +17920,7 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S259" s="1" t="n">
@@ -17987,7 +17987,7 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S260" s="1" t="n">
@@ -18054,7 +18054,7 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S261" s="1" t="n">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S262" s="1" t="n">
@@ -18188,7 +18188,7 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S263" s="1" t="n">
@@ -18255,7 +18255,7 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S264" s="1" t="n">
@@ -18322,7 +18322,7 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S265" s="1" t="n">
@@ -18389,7 +18389,7 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S266" s="1" t="n">
@@ -18456,7 +18456,7 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S267" s="1" t="n">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S268" s="1" t="n">
@@ -18590,7 +18590,7 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S269" s="1" t="n">
@@ -18657,7 +18657,7 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S270" s="1" t="n">
@@ -18724,7 +18724,7 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S271" s="1" t="n">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S272" s="1" t="n">
@@ -18858,7 +18858,7 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S273" s="1" t="n">
@@ -18925,7 +18925,7 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S274" s="1" t="n">
@@ -18992,7 +18992,7 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S275" s="1" t="n">
@@ -19059,7 +19059,7 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S276" s="1" t="n">
@@ -19126,7 +19126,7 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S277" s="1" t="n">
@@ -19193,7 +19193,7 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S278" s="1" t="n">
@@ -19260,7 +19260,7 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S279" s="1" t="n">
@@ -19327,7 +19327,7 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S280" s="1" t="n">
@@ -19394,7 +19394,7 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S281" s="1" t="n">
@@ -19461,7 +19461,7 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S282" s="1" t="n">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S283" s="1" t="n">
@@ -19595,7 +19595,7 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S284" s="1" t="n">
@@ -19662,7 +19662,7 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S285" s="1" t="n">
@@ -19729,7 +19729,7 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S286" s="1" t="n">
@@ -19796,7 +19796,7 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S287" s="1" t="n">
@@ -19863,7 +19863,7 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S288" s="1" t="n">
@@ -19930,7 +19930,7 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S289" s="1" t="n">
@@ -19997,7 +19997,7 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S290" s="1" t="n">
@@ -20064,7 +20064,7 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S291" s="1" t="n">
@@ -20131,7 +20131,7 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S292" s="1" t="n">
@@ -20198,7 +20198,7 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S293" s="1" t="n">
@@ -20265,7 +20265,7 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S294" s="1" t="n">
@@ -20332,7 +20332,7 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S295" s="1" t="n">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S296" s="1" t="n">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S297" s="1" t="n">
@@ -20533,7 +20533,7 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S298" s="1" t="n">
@@ -20600,7 +20600,7 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S299" s="1" t="n">
@@ -20667,7 +20667,7 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S300" s="1" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S301" s="1" t="n">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S302" s="1" t="n">
@@ -20868,7 +20868,7 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S303" s="1" t="n">
@@ -20935,7 +20935,7 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S304" s="1" t="n">
@@ -21002,7 +21002,7 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S305" s="1" t="n">
@@ -21069,7 +21069,7 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S306" s="1" t="n">
@@ -21136,7 +21136,7 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S307" s="1" t="n">
@@ -21203,7 +21203,7 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S308" s="1" t="n">
@@ -21270,7 +21270,7 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S309" s="1" t="n">
@@ -21337,7 +21337,7 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S310" s="1" t="n">
@@ -21404,7 +21404,7 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S311" s="1" t="n">
@@ -21471,7 +21471,7 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S312" s="1" t="n">
@@ -21538,7 +21538,7 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S313" s="1" t="n">
@@ -21605,7 +21605,7 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S314" s="1" t="n">
@@ -21672,7 +21672,7 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S315" s="1" t="n">
@@ -21739,7 +21739,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S316" s="1" t="n">
@@ -21806,7 +21806,7 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S317" s="1" t="n">
@@ -21873,7 +21873,7 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S318" s="1" t="n">
@@ -21940,7 +21940,7 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S319" s="1" t="n">
@@ -22007,7 +22007,7 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S320" s="1" t="n">
@@ -22074,7 +22074,7 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S321" s="1" t="n">
@@ -22141,7 +22141,7 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S322" s="1" t="n">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S323" s="1" t="n">
@@ -22275,7 +22275,7 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S324" s="1" t="n">
@@ -22342,7 +22342,7 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S325" s="1" t="n">
@@ -22409,7 +22409,7 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S326" s="1" t="n">
@@ -22476,7 +22476,7 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S327" s="1" t="n">
@@ -22543,7 +22543,7 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S328" s="1" t="n">
@@ -22610,7 +22610,7 @@
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S329" s="1" t="n">
@@ -22677,7 +22677,7 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S330" s="1" t="n">
@@ -22744,7 +22744,7 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S331" s="1" t="n">
@@ -22811,7 +22811,7 @@
       </c>
       <c r="R332" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S332" s="1" t="n">
@@ -22878,7 +22878,7 @@
       </c>
       <c r="R333" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S333" s="1" t="n">
@@ -22945,7 +22945,7 @@
       </c>
       <c r="R334" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S334" s="1" t="n">
@@ -23012,7 +23012,7 @@
       </c>
       <c r="R335" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S335" s="1" t="n">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="R336" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S336" s="1" t="n">
@@ -23146,7 +23146,7 @@
       </c>
       <c r="R337" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S337" s="1" t="n">
@@ -23213,7 +23213,7 @@
       </c>
       <c r="R338" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S338" s="1" t="n">
@@ -23280,7 +23280,7 @@
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S339" s="1" t="n">
@@ -23347,7 +23347,7 @@
       </c>
       <c r="R340" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S340" s="1" t="n">
@@ -23398,7 +23398,7 @@
       </c>
       <c r="R341" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S341" t="inlineStr"/>
@@ -23447,7 +23447,7 @@
       </c>
       <c r="R342" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S342" t="inlineStr"/>
@@ -23496,7 +23496,7 @@
       </c>
       <c r="R343" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S343" t="inlineStr"/>
@@ -23545,7 +23545,7 @@
       </c>
       <c r="R344" t="inlineStr">
         <is>
-          <t>2026-10-01 10:25:14</t>
+          <t>2026-10-01 15:39:37</t>
         </is>
       </c>
       <c r="S344" t="inlineStr"/>
